--- a/data/trans_dic/P44A$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -615,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -625,47 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -678,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,69; 29,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,29; 69,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,92; 78,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,42; 49,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,55; 37,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -735,47 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8,28; 39,25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15,32; 40,31</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13,84; 47,97</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,18; 40,89</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,18; 36,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,99; 35,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -845,47 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -898,54 +898,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,57; 47,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,38; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,04; 51,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,36; 43,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,57; 29,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,67; 39,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,33; 1,98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -955,47 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1008,54 +1008,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,55</t>
+          <t>12,66; 49,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 29,16</t>
+          <t>7,2; 32,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 69,29</t>
+          <t>15,53; 58,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,61; 79,81</t>
+          <t>9,44; 44,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,49; 49,11</t>
+          <t>20,2; 47,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 38,51</t>
+          <t>11,58; 31,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1065,47 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1118,389 +1118,59 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 38,06</t>
+          <t>9,85; 25,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,84; 40,36</t>
+          <t>16,52; 30,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>0,07; 1,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 49,19</t>
+          <t>26,28; 46,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 42,11</t>
+          <t>18,11; 35,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>0,12; 1,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,72; 36,45</t>
+          <t>19,3; 32,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 35,57</t>
+          <t>19,07; 29,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>0,17; 0,85</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>30,58%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 22,75</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>17,78; 46,87</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 3,49</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15,91; 49,3</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 44,34</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,31</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>10,3; 30,24</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>19,24; 40,39</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 2,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17,62%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>12,46; 49,45</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8,05; 33,25</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,25</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17,14; 62,45</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8,46; 42,87</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,41</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,61; 46,3</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11,45; 30,53</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>22,81%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>26,06%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>24,18%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 24,91</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16,66; 30,06</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 1,05</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>25,06; 44,39</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17,96; 34,86</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 1,24</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18,96; 31,91</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>19,62; 30,37</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 0,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -1508,11 +1178,8 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1634,7 +1301,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1644,47 +1311,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1364,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2189</t>
         </is>
       </c>
     </row>
@@ -1750,54 +1417,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4619</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>988; 7860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 7862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5391; 14223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1867; 8702</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5693; 17102</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3989; 14033</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 8834</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1807,42 +1474,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1860,47 +1527,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1913,42 +1580,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3259; 15440</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8025; 21120</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4673; 16196</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4229; 15474</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10368; 26425</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14425; 32359</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1960,7 +1627,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1970,47 +1637,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2023,47 +1690,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2714</t>
         </is>
       </c>
     </row>
@@ -2076,54 +1743,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 7409</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8153; 20671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>631; 5950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5034; 16026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3543; 13707</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2531</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5932; 18463</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14023; 29313</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1001; 6072</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2133,47 +1800,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -2186,47 +1853,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>596</t>
         </is>
       </c>
     </row>
@@ -2239,54 +1906,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4613</t>
+          <t>3196; 12381</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>968; 7809</t>
+          <t>2634; 11791</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7733</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5475; 14211</t>
+          <t>3306; 12414</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1944; 8809</t>
+          <t>3403; 16009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 3272</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5720; 17031</t>
+          <t>9398; 22089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4077; 14563</t>
+          <t>8414; 23047</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 8799</t>
+          <t>0; 2950</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2296,47 +1963,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2349,47 +2016,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>37283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>55176</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5499</t>
         </is>
       </c>
     </row>
@@ -2402,559 +2069,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3185; 14974</t>
+          <t>10773; 27710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7774; 21148</t>
+          <t>26384; 47921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1613</t>
+          <t>516; 8265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4178; 16608</t>
+          <t>28103; 50006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4243; 15934</t>
+          <t>21031; 40709</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1064</t>
+          <t>594; 5537</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10029; 26645</t>
+          <t>41755; 70122</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14178; 32096</t>
+          <t>52593; 82205</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1307</t>
+          <t>2137; 10686</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13427</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9574</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8054</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11672</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>21481</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>0; 6965</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7809; 20582</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>618; 5725</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>4992; 15472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>3987; 13831</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 1871</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6384; 18746</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14447; 30337</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>986; 6509</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>6449</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7844</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15099</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>14294</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>3144; 12481</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2947; 12169</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0; 1209</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3649; 13298</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3051; 15457</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0; 2601</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8658; 21546</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8318; 22182</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>0; 3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>17892</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>36425</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>37283</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>30257</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>55176</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>66682</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>5499</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>10251; 27241</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>26601; 47997</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>509; 8172</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>26798; 47477</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>20859; 40485</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>747; 5927</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>41016; 69024</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>54103; 83751</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2053; 11182</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P44A$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,59</t>
+          <t>0,0; 35,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 29,35</t>
+          <t>3,67; 29,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 69,35</t>
+          <t>26,66; 69,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 78,84</t>
+          <t>16,11; 79,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,42; 49,31</t>
+          <t>16,48; 48,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 37,11</t>
+          <t>10,74; 38,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,25; 3,98</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 39,25</t>
+          <t>7,96; 35,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,32; 40,31</t>
+          <t>13,87; 40,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 47,97</t>
+          <t>15,82; 51,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 40,89</t>
+          <t>11,04; 41,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 36,15</t>
+          <t>13,51; 35,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 35,86</t>
+          <t>16,2; 35,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,2</t>
+          <t>0,0; 21,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,57; 47,07</t>
+          <t>17,77; 47,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,63</t>
+          <t>0,32; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 51,07</t>
+          <t>15,72; 47,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 43,94</t>
+          <t>12,18; 43,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 29,78</t>
+          <t>10,61; 30,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 39,03</t>
+          <t>18,95; 40,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,98</t>
+          <t>0,27; 1,82</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 49,05</t>
+          <t>12,38; 45,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 32,22</t>
+          <t>8,36; 32,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 58,3</t>
+          <t>16,53; 58,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 44,4</t>
+          <t>9,56; 39,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,2; 47,47</t>
+          <t>18,18; 46,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 31,72</t>
+          <t>11,24; 32,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 25,34</t>
+          <t>9,48; 25,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 30,01</t>
+          <t>16,79; 30,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,06</t>
+          <t>0,2; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 46,76</t>
+          <t>25,5; 44,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 35,06</t>
+          <t>18,16; 35,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,16</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 32,42</t>
+          <t>19,54; 32,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 29,8</t>
+          <t>19,02; 29,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,85</t>
+          <t>0,27; 1,11</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2280</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4619</t>
+          <t>0; 5067</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>988; 7860</t>
+          <t>982; 7788</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7862</t>
+          <t>0; 5613</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5391; 14223</t>
+          <t>5467; 14315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1867; 8702</t>
+          <t>1778; 8733</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4483</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5693; 17102</t>
+          <t>5715; 16845</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3989; 14033</t>
+          <t>4061; 14717</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 8834</t>
+          <t>431; 6837</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3259; 15440</t>
+          <t>3130; 13882</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8025; 21120</t>
+          <t>7268; 21355</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4673; 16196</t>
+          <t>5340; 17385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4229; 15474</t>
+          <t>4179; 15868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10368; 26425</t>
+          <t>9879; 26231</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14425; 32359</t>
+          <t>14616; 32452</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2726</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7409</t>
+          <t>0; 6631</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8153; 20671</t>
+          <t>7805; 20826</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631; 5950</t>
+          <t>570; 5688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5034; 16026</t>
+          <t>4933; 14923</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3543; 13707</t>
+          <t>3798; 13512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2531</t>
+          <t>0; 1898</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5932; 18463</t>
+          <t>6575; 19105</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14023; 29313</t>
+          <t>14232; 30137</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1001; 6072</t>
+          <t>911; 6086</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>660</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3196; 12381</t>
+          <t>3126; 11553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2634; 11791</t>
+          <t>3059; 12045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,32 +1921,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3306; 12414</t>
+          <t>3520; 12407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3403; 16009</t>
+          <t>3447; 14293</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3272</t>
+          <t>0; 3267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9398; 22089</t>
+          <t>8460; 21782</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8414; 23047</t>
+          <t>8165; 23402</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2950</t>
+          <t>0; 3308</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10773; 27710</t>
+          <t>10363; 27833</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26384; 47921</t>
+          <t>26818; 48850</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>516; 8265</t>
+          <t>1134; 8062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28103; 50006</t>
+          <t>27274; 47331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21031; 40709</t>
+          <t>21083; 41399</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>594; 5537</t>
+          <t>656; 5722</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41755; 70122</t>
+          <t>42263; 69254</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52593; 82205</t>
+          <t>52459; 81742</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2137; 10686</t>
+          <t>2978; 12210</t>
         </is>
       </c>
     </row>
